--- a/bs_v2.xlsx
+++ b/bs_v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupohsgp-my.sharepoint.com/personal/guilherme_oliveira_hpmobilidade_com_br/Documents/Documentos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AFD2F814-5D08-4167-BAB8-3573A90D2667}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{AFD2F814-5D08-4167-BAB8-3573A90D2667}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8451D6C8-58B0-4B10-9161-E807801F0EEC}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{DB2EE364-8156-43FA-8926-BE681F87A7C8}"/>
+    <workbookView xWindow="-30828" yWindow="0" windowWidth="30936" windowHeight="16776" xr2:uid="{DB2EE364-8156-43FA-8926-BE681F87A7C8}"/>
   </bookViews>
   <sheets>
     <sheet name="bs" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3191" uniqueCount="3124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3199" uniqueCount="3131">
   <si>
     <t>id</t>
   </si>
@@ -9411,6 +9411,27 @@
   </si>
   <si>
     <t xml:space="preserve"> 179 </t>
+  </si>
+  <si>
+    <t>9F2F431A</t>
+  </si>
+  <si>
+    <t>GUILHERME OLIVIERA</t>
+  </si>
+  <si>
+    <t>3A212A79</t>
+  </si>
+  <si>
+    <t>3A2570B9</t>
+  </si>
+  <si>
+    <t>NATALIA LARA</t>
+  </si>
+  <si>
+    <t>999+</t>
+  </si>
+  <si>
+    <t>NOME SOBRENOME</t>
   </si>
 </sst>
 </file>
@@ -9824,7 +9845,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{693BEBBF-AF8F-4FD8-BC9B-5AB67C9746A0}">
-  <dimension ref="A1:E829"/>
+  <dimension ref="A1:E832"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="9.921875" bestFit="1" customWidth="1"/>
@@ -23927,6 +23948,57 @@
         <v>3123</v>
       </c>
     </row>
+    <row r="830" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A830" t="s">
+        <v>3124</v>
+      </c>
+      <c r="B830">
+        <v>18725</v>
+      </c>
+      <c r="C830" t="s">
+        <v>3125</v>
+      </c>
+      <c r="D830">
+        <v>15000</v>
+      </c>
+      <c r="E830">
+        <v>57000</v>
+      </c>
+    </row>
+    <row r="831" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A831" t="s">
+        <v>3126</v>
+      </c>
+      <c r="B831">
+        <v>1</v>
+      </c>
+      <c r="C831" t="s">
+        <v>3130</v>
+      </c>
+      <c r="D831">
+        <v>1</v>
+      </c>
+      <c r="E831">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="832" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A832" t="s">
+        <v>3127</v>
+      </c>
+      <c r="B832">
+        <v>19736</v>
+      </c>
+      <c r="C832" t="s">
+        <v>3128</v>
+      </c>
+      <c r="D832" t="s">
+        <v>3129</v>
+      </c>
+      <c r="E832" t="s">
+        <v>3129</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A829">
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>

--- a/bs_v2.xlsx
+++ b/bs_v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupohsgp-my.sharepoint.com/personal/guilherme_oliveira_hpmobilidade_com_br/Documents/Documentos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{AFD2F814-5D08-4167-BAB8-3573A90D2667}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8451D6C8-58B0-4B10-9161-E807801F0EEC}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="8_{AFD2F814-5D08-4167-BAB8-3573A90D2667}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4DB0526E-BB60-4F47-BFCD-1BFB90A5C781}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="0" windowWidth="30936" windowHeight="16776" xr2:uid="{DB2EE364-8156-43FA-8926-BE681F87A7C8}"/>
+    <workbookView xWindow="5494" yWindow="3540" windowWidth="16449" windowHeight="9454" xr2:uid="{DB2EE364-8156-43FA-8926-BE681F87A7C8}"/>
   </bookViews>
   <sheets>
     <sheet name="bs" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3199" uniqueCount="3131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3201" uniqueCount="3133">
   <si>
     <t>id</t>
   </si>
@@ -9432,6 +9432,12 @@
   </si>
   <si>
     <t>NOME SOBRENOME</t>
+  </si>
+  <si>
+    <t>15.000</t>
+  </si>
+  <si>
+    <t>57.000</t>
   </si>
 </sst>
 </file>
@@ -9478,7 +9484,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -9489,6 +9495,7 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -23958,11 +23965,11 @@
       <c r="C830" t="s">
         <v>3125</v>
       </c>
-      <c r="D830">
-        <v>15000</v>
-      </c>
-      <c r="E830">
-        <v>57000</v>
+      <c r="D830" s="4" t="s">
+        <v>3131</v>
+      </c>
+      <c r="E830" s="4" t="s">
+        <v>3132</v>
       </c>
     </row>
     <row r="831" spans="1:5" x14ac:dyDescent="0.4">
